--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M9B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M9B1_IN_Piura.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.07</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>11.99</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C13" s="29">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>65.46</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>21.88</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1917,11 +1917,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>355.3638</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>2.3809</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.67</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>352.9829</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.33</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>355.5677</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2288,6 +2288,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2372,6 +2373,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2416,6 +2418,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="168" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2635,11 +2638,11 @@
       </c>
       <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>814.65</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2649,19 +2652,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>19.84</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.441</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>28.68</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>64.19</v>
       </c>
     </row>
     <row r="13"/>
